--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487569_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487569_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>D. DIARRA</t>
+          <t>. SUAREZ HEVIA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,67 +565,67 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.0895</v>
+        <v>3.0802</v>
       </c>
       <c r="E2" t="n">
-        <v>5.5109</v>
+        <v>3.8037</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4214</v>
+        <v>-0.7235</v>
       </c>
       <c r="G2" t="n">
-        <v>-3.6567</v>
+        <v>0.0435</v>
       </c>
       <c r="H2" t="n">
-        <v>-0.4339</v>
+        <v>1.5236</v>
       </c>
       <c r="I2" t="n">
-        <v>-3.2228</v>
+        <v>-1.4802</v>
       </c>
       <c r="J2" t="n">
-        <v>0.6473</v>
+        <v>2.6694</v>
       </c>
       <c r="K2" t="n">
-        <v>0.9254</v>
+        <v>2.5433</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.2781</v>
+        <v>0.1261</v>
       </c>
       <c r="M2" t="n">
-        <v>-4.304</v>
+        <v>-2.6259</v>
       </c>
       <c r="N2" t="n">
-        <v>-1.3593</v>
+        <v>-1.0197</v>
       </c>
       <c r="O2" t="n">
-        <v>-2.9447</v>
+        <v>-1.6062</v>
       </c>
       <c r="P2" t="n">
-        <v>3.3294</v>
+        <v>2.7419</v>
       </c>
       <c r="Q2" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>4.3087</v>
+        <v>2.7419</v>
       </c>
       <c r="S2" t="n">
-        <v>5.4168</v>
+        <v>-0.3135</v>
       </c>
       <c r="T2" t="n">
-        <v>4.6263</v>
+        <v>-0.0823</v>
       </c>
       <c r="U2" t="n">
-        <v>0.7906</v>
+        <v>-0.2311</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>0.6083</v>
       </c>
       <c r="W2" t="n">
         <v>1.2166</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.2166</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="3">
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.6029</v>
+        <v>2.9179</v>
       </c>
       <c r="E3" t="n">
-        <v>4.0445</v>
+        <v>3.2259</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4416</v>
+        <v>-0.308</v>
       </c>
       <c r="G3" t="n">
         <v>0.7261</v>
@@ -688,13 +688,13 @@
         <v>2.546</v>
       </c>
       <c r="S3" t="n">
-        <v>0.6637</v>
+        <v>-0.0213</v>
       </c>
       <c r="T3" t="n">
-        <v>1.0963</v>
+        <v>0.2776</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4326</v>
+        <v>-0.2989</v>
       </c>
       <c r="V3" t="n">
         <v>-0.3329</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>. SUAREZ HEVIA</t>
+          <t>A. MIRANDA GARCIA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.4616</v>
+        <v>2.6983</v>
       </c>
       <c r="E4" t="n">
-        <v>3.292</v>
+        <v>2.0497</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.8304</v>
+        <v>0.6486</v>
       </c>
       <c r="G4" t="n">
-        <v>0.0435</v>
+        <v>2.0518</v>
       </c>
       <c r="H4" t="n">
-        <v>1.5236</v>
+        <v>0.2987</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.4802</v>
+        <v>1.7531</v>
       </c>
       <c r="J4" t="n">
-        <v>2.6694</v>
+        <v>3.8694</v>
       </c>
       <c r="K4" t="n">
-        <v>2.5433</v>
+        <v>1.3184</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1261</v>
+        <v>2.551</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.6259</v>
+        <v>-1.8176</v>
       </c>
       <c r="N4" t="n">
         <v>-1.0197</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.6062</v>
+        <v>-0.7979000000000001</v>
       </c>
       <c r="P4" t="n">
-        <v>2.7419</v>
+        <v>0.7834</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R4" t="n">
         <v>2.7419</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.9321</v>
+        <v>-0.1369</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.594</v>
+        <v>0.1388</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3381</v>
+        <v>-0.2757</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6083</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.6083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. MIRANDA GARCIA</t>
+          <t>R. FERNANDEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.0041</v>
+        <v>1.7438</v>
       </c>
       <c r="E5" t="n">
-        <v>1.4357</v>
+        <v>3.1813</v>
       </c>
       <c r="F5" t="n">
-        <v>0.5684</v>
+        <v>-1.4375</v>
       </c>
       <c r="G5" t="n">
-        <v>2.0518</v>
+        <v>-0.9011</v>
       </c>
       <c r="H5" t="n">
-        <v>0.2987</v>
+        <v>-0.5975</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7531</v>
+        <v>-0.3037</v>
       </c>
       <c r="J5" t="n">
-        <v>3.8694</v>
+        <v>2.9404</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3184</v>
+        <v>1.1024</v>
       </c>
       <c r="L5" t="n">
-        <v>2.551</v>
+        <v>1.838</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.8176</v>
+        <v>-3.8415</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.0197</v>
+        <v>-1.6999</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.7979000000000001</v>
+        <v>-2.1416</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7834</v>
+        <v>1.5668</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7419</v>
+        <v>2.546</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.8310999999999999</v>
+        <v>-0.1385</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.4752</v>
+        <v>0.0035</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3559</v>
+        <v>-0.142</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.2166</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5766</v>
+        <v>1.7057</v>
       </c>
       <c r="E6" t="n">
-        <v>2.0554</v>
+        <v>2.1578</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4788</v>
+        <v>-0.4521</v>
       </c>
       <c r="G6" t="n">
         <v>3.7335</v>
@@ -922,13 +922,13 @@
         <v>2.1543</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.3562</v>
+        <v>-0.2272</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.1494</v>
+        <v>-0.0471</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2068</v>
+        <v>-0.1801</v>
       </c>
       <c r="V6" t="n">
         <v>0.9412</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. FERNANDEZ FERNANDEZ</t>
+          <t>D. DIARRA</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.867</v>
+        <v>1.5918</v>
       </c>
       <c r="E7" t="n">
-        <v>2.4649</v>
+        <v>2.4408</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.5979</v>
+        <v>-0.8491</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.9011</v>
+        <v>-3.6567</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.5975</v>
+        <v>-0.4339</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3037</v>
+        <v>-3.2228</v>
       </c>
       <c r="J7" t="n">
-        <v>2.9404</v>
+        <v>0.6473</v>
       </c>
       <c r="K7" t="n">
-        <v>1.1024</v>
+        <v>0.9254</v>
       </c>
       <c r="L7" t="n">
-        <v>1.838</v>
+        <v>-0.2781</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.8415</v>
+        <v>-4.304</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.6999</v>
+        <v>-1.3593</v>
       </c>
       <c r="O7" t="n">
-        <v>-2.1416</v>
+        <v>-2.9447</v>
       </c>
       <c r="P7" t="n">
-        <v>1.5668</v>
+        <v>3.3294</v>
       </c>
       <c r="Q7" t="n">
         <v>-0.9792</v>
       </c>
       <c r="R7" t="n">
-        <v>2.546</v>
+        <v>4.3087</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.0152</v>
+        <v>1.9191</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7128</v>
+        <v>1.5562</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3024</v>
+        <v>0.3629</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2166</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
         <v>1.2166</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.2982</v>
+        <v>0.1065</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0884</v>
+        <v>-1.5767</v>
       </c>
       <c r="F8" t="n">
-        <v>1.7902</v>
+        <v>1.6833</v>
       </c>
       <c r="G8" t="n">
         <v>-1.6796</v>
@@ -1078,13 +1078,13 @@
         <v>3.1336</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.8306</v>
+        <v>-0.4258</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8316</v>
+        <v>-0.3199</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0011</v>
+        <v>-0.1059</v>
       </c>
       <c r="V8" t="n">
         <v>0.0576</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. QUIROS HERNANDEZ</t>
+          <t>M. BARTOLOME COBLE</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.6415</v>
+        <v>-1.3327</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6589</v>
+        <v>-0.8905999999999999</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0175</v>
+        <v>-0.442</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.5503</v>
+        <v>-3.8318</v>
       </c>
       <c r="H9" t="n">
-        <v>-2.0705</v>
+        <v>-1.2849</v>
       </c>
       <c r="I9" t="n">
-        <v>0.5202</v>
+        <v>-2.5469</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.9461000000000001</v>
+        <v>-0.1309</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.9153</v>
+        <v>0.0067</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.0308</v>
+        <v>-0.1376</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.6041</v>
+        <v>-3.7009</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.1551</v>
+        <v>-1.2916</v>
       </c>
       <c r="O9" t="n">
-        <v>0.551</v>
+        <v>-2.4093</v>
       </c>
       <c r="P9" t="n">
-        <v>1.1751</v>
+        <v>2.3502</v>
       </c>
       <c r="Q9" t="n">
+        <v>-0.9792</v>
+      </c>
+      <c r="R9" t="n">
+        <v>3.3294</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.1265</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-0.0559</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.0706</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.2754</v>
+      </c>
+      <c r="X9" t="n">
         <v>0</v>
-      </c>
-      <c r="R9" t="n">
-        <v>1.1751</v>
-      </c>
-      <c r="S9" t="n">
-        <v>-0.9909</v>
-      </c>
-      <c r="T9" t="n">
-        <v>-0.7128</v>
-      </c>
-      <c r="U9" t="n">
-        <v>-0.2781</v>
-      </c>
-      <c r="V9" t="n">
-        <v>-0.2754</v>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>-0.2754</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.0079</v>
+        <v>-1.4962</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.6311</v>
+        <v>-1.1194</v>
       </c>
       <c r="F10" t="n">
         <v>-0.3768</v>
@@ -1234,10 +1234,10 @@
         <v>2.7419</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.098</v>
+        <v>-0.5864</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.0098</v>
+        <v>-0.4982</v>
       </c>
       <c r="U10" t="n">
         <v>-0.0882</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>M. BARTOLOME COBLE</t>
+          <t>R. QUIROS HERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.156</v>
+        <v>-1.517</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.607</v>
+        <v>-1.4543</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.549</v>
+        <v>-0.06270000000000001</v>
       </c>
       <c r="G11" t="n">
-        <v>-3.8318</v>
+        <v>-1.5503</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.2849</v>
+        <v>-2.0705</v>
       </c>
       <c r="I11" t="n">
-        <v>-2.5469</v>
+        <v>0.5202</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1309</v>
+        <v>-0.9461000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0067</v>
+        <v>-0.9153</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.1376</v>
+        <v>-0.0308</v>
       </c>
       <c r="M11" t="n">
-        <v>-3.7009</v>
+        <v>-0.6041</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2916</v>
+        <v>-1.1551</v>
       </c>
       <c r="O11" t="n">
-        <v>-2.4093</v>
+        <v>0.551</v>
       </c>
       <c r="P11" t="n">
-        <v>2.3502</v>
+        <v>1.1751</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>3.3294</v>
+        <v>1.1751</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.9497</v>
+        <v>-0.8665</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.7722</v>
+        <v>-0.5082</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1775</v>
+        <v>-0.3583</v>
       </c>
       <c r="V11" t="n">
-        <v>0.2754</v>
+        <v>-0.2754</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="12">
@@ -1345,16 +1345,16 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>9.498099999999999</v>
+        <v>9.498300000000002</v>
       </c>
       <c r="E12" t="n">
-        <v>11.818</v>
+        <v>11.8182</v>
       </c>
       <c r="F12" t="n">
         <v>-2.3198</v>
       </c>
       <c r="G12" t="n">
-        <v>-6.853400000000001</v>
+        <v>-6.8534</v>
       </c>
       <c r="H12" t="n">
         <v>-5.463200000000001</v>
@@ -1390,10 +1390,10 @@
         <v>27.4188</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9232999999999987</v>
+        <v>-0.9235000000000001</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4647999999999994</v>
+        <v>0.4645000000000004</v>
       </c>
       <c r="U12" t="n">
         <v>-1.3879</v>
@@ -1402,7 +1402,7 @@
         <v>1.6071</v>
       </c>
       <c r="W12" t="n">
-        <v>5.4172</v>
+        <v>5.417199999999999</v>
       </c>
       <c r="X12" t="n">
         <v>-3.8101</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>6.4363</v>
+        <v>7.2061</v>
       </c>
       <c r="E13" t="n">
-        <v>6.9563</v>
+        <v>7.6727</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.52</v>
+        <v>-0.4665</v>
       </c>
       <c r="G13" t="n">
         <v>5.0179</v>
@@ -1468,13 +1468,13 @@
         <v>1.3709</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.09429999999999999</v>
+        <v>0.6755</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.4752</v>
+        <v>0.2411</v>
       </c>
       <c r="U13" t="n">
-        <v>0.3809</v>
+        <v>0.4343</v>
       </c>
       <c r="V13" t="n">
         <v>2.1003</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.8088</v>
+        <v>3.417</v>
       </c>
       <c r="E14" t="n">
-        <v>5.456</v>
+        <v>5.2513</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.6472</v>
+        <v>-1.8343</v>
       </c>
       <c r="G14" t="n">
         <v>1.6795</v>
@@ -1546,13 +1546,13 @@
         <v>1.1751</v>
       </c>
       <c r="S14" t="n">
-        <v>1.1756</v>
+        <v>0.7838000000000001</v>
       </c>
       <c r="T14" t="n">
-        <v>0.4734</v>
+        <v>0.2688</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7022</v>
+        <v>0.5151</v>
       </c>
       <c r="V14" t="n">
         <v>-0.0255</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>J. LUIS</t>
+          <t>E. OGUNFOLU</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.5044</v>
+        <v>0.8498</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5421</v>
+        <v>0.7282</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.0378</v>
+        <v>0.1217</v>
       </c>
       <c r="G15" t="n">
-        <v>1.5069</v>
+        <v>3.0781</v>
       </c>
       <c r="H15" t="n">
-        <v>0.2181</v>
+        <v>2.2746</v>
       </c>
       <c r="I15" t="n">
-        <v>1.2888</v>
+        <v>0.8035</v>
       </c>
       <c r="J15" t="n">
-        <v>3.0986</v>
+        <v>3.877</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3504</v>
+        <v>3.2256</v>
       </c>
       <c r="L15" t="n">
-        <v>2.7482</v>
+        <v>0.6515</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.5917</v>
+        <v>-0.799</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1323</v>
+        <v>-0.951</v>
       </c>
       <c r="O15" t="n">
-        <v>-1.4594</v>
+        <v>0.152</v>
       </c>
       <c r="P15" t="n">
-        <v>-1.7626</v>
+        <v>-2.1543</v>
       </c>
       <c r="Q15" t="n">
-        <v>-2.9377</v>
+        <v>-3.3294</v>
       </c>
       <c r="R15" t="n">
         <v>1.1751</v>
       </c>
       <c r="S15" t="n">
-        <v>1.4847</v>
+        <v>0.1694</v>
       </c>
       <c r="T15" t="n">
-        <v>0.8893</v>
+        <v>0.1806</v>
       </c>
       <c r="U15" t="n">
-        <v>0.5954</v>
+        <v>-0.0112</v>
       </c>
       <c r="V15" t="n">
-        <v>0.2754</v>
+        <v>-0.2433</v>
       </c>
       <c r="W15" t="n">
-        <v>1.492</v>
+        <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>-1.2166</v>
+        <v>-0.2433</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>E. OGUNFOLU</t>
+          <t>J. LUIS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2683</v>
+        <v>0.3023</v>
       </c>
       <c r="E16" t="n">
-        <v>0.9328</v>
+        <v>1.9281</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3355</v>
+        <v>-1.6258</v>
       </c>
       <c r="G16" t="n">
-        <v>3.0781</v>
+        <v>1.5069</v>
       </c>
       <c r="H16" t="n">
-        <v>2.2746</v>
+        <v>0.2181</v>
       </c>
       <c r="I16" t="n">
-        <v>0.8035</v>
+        <v>1.2888</v>
       </c>
       <c r="J16" t="n">
-        <v>3.877</v>
+        <v>3.0986</v>
       </c>
       <c r="K16" t="n">
-        <v>3.2256</v>
+        <v>0.3504</v>
       </c>
       <c r="L16" t="n">
-        <v>0.6515</v>
+        <v>2.7482</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.799</v>
+        <v>-1.5917</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.951</v>
+        <v>-0.1323</v>
       </c>
       <c r="O16" t="n">
-        <v>0.152</v>
+        <v>-1.4594</v>
       </c>
       <c r="P16" t="n">
-        <v>-2.1543</v>
+        <v>-1.7626</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.3294</v>
+        <v>-2.9377</v>
       </c>
       <c r="R16" t="n">
         <v>1.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>0.5879</v>
+        <v>0.2826</v>
       </c>
       <c r="T16" t="n">
-        <v>0.3852</v>
+        <v>0.2752</v>
       </c>
       <c r="U16" t="n">
-        <v>0.2027</v>
+        <v>0.0074</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.2433</v>
+        <v>0.2754</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>1.492</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2433</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="17">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.491</v>
+        <v>-0.4376</v>
       </c>
       <c r="E17" t="n">
         <v>-0.1117</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.3793</v>
+        <v>-0.3258</v>
       </c>
       <c r="G17" t="n">
         <v>2.1165</v>
@@ -1780,13 +1780,13 @@
         <v>0.1958</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.5695</v>
+        <v>-0.5161</v>
       </c>
       <c r="T17" t="n">
         <v>-0.0594</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5101</v>
+        <v>-0.4567</v>
       </c>
       <c r="V17" t="n">
         <v>-0.2754</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-4.522</v>
+        <v>-4.0454</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.9546</v>
+        <v>-1.8523</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5674</v>
+        <v>-2.1931</v>
       </c>
       <c r="G18" t="n">
         <v>-3.1365</v>
@@ -1858,13 +1858,13 @@
         <v>1.5668</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7298</v>
+        <v>-0.2532</v>
       </c>
       <c r="T18" t="n">
-        <v>0.0882</v>
+        <v>0.1906</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.8179999999999999</v>
+        <v>-0.4437</v>
       </c>
       <c r="V18" t="n">
         <v>-0.8516</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-4.7673</v>
+        <v>-4.7314</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.8008</v>
+        <v>-3.0055</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.9665</v>
+        <v>-1.7259</v>
       </c>
       <c r="G19" t="n">
         <v>-1.515</v>
@@ -1936,13 +1936,13 @@
         <v>1.1751</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.0772</v>
+        <v>-0.0413</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4446</v>
+        <v>0.24</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5219</v>
+        <v>-0.2813</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2166</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-5.4753</v>
+        <v>-4.9414</v>
       </c>
       <c r="E20" t="n">
-        <v>-3.5595</v>
+        <v>-2.9455</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.9157</v>
+        <v>-1.9959</v>
       </c>
       <c r="G20" t="n">
         <v>1.2778</v>
@@ -2014,13 +2014,13 @@
         <v>1.5668</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5928</v>
+        <v>-0.059</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.7722</v>
+        <v>-0.1582</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1794</v>
+        <v>0.0993</v>
       </c>
       <c r="V20" t="n">
         <v>-1.4599</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-7.2604</v>
+        <v>-7.1176</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.1407</v>
+        <v>-5.3454</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.1197</v>
+        <v>-1.7722</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1718</v>
@@ -2092,13 +2092,13 @@
         <v>2.3502</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.2612</v>
+        <v>-0.1184</v>
       </c>
       <c r="T21" t="n">
-        <v>0.414</v>
+        <v>0.2094</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6752</v>
+        <v>-0.3277</v>
       </c>
       <c r="V21" t="n">
         <v>0.0896</v>
@@ -2128,10 +2128,10 @@
         <v>-9.498199999999997</v>
       </c>
       <c r="E22" t="n">
-        <v>2.3199</v>
+        <v>2.319899999999999</v>
       </c>
       <c r="F22" t="n">
-        <v>-11.8181</v>
+        <v>-11.8178</v>
       </c>
       <c r="G22" t="n">
         <v>6.8534</v>
@@ -2170,13 +2170,13 @@
         <v>11.7509</v>
       </c>
       <c r="S22" t="n">
-        <v>0.9234000000000001</v>
+        <v>0.9233</v>
       </c>
       <c r="T22" t="n">
-        <v>1.3879</v>
+        <v>1.3881</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4646000000000001</v>
+        <v>-0.4645</v>
       </c>
       <c r="V22" t="n">
         <v>-1.607</v>
